--- a/artfynd/A 49168-2024 artfynd.xlsx
+++ b/artfynd/A 49168-2024 artfynd.xlsx
@@ -2237,10 +2237,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121186445</v>
+        <v>121185780</v>
       </c>
       <c r="B16" t="n">
-        <v>82382</v>
+        <v>57348</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2253,26 +2253,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2280,10 +2285,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>698474</v>
+        <v>698280</v>
       </c>
       <c r="R16" t="n">
-        <v>7310500</v>
+        <v>7310466</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2318,13 +2323,17 @@
           <t>2024-11-14</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Björk med fyra bohål, varav en är nyligen avänt. Färsk sågspån på marken.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2336,17 +2345,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Peter Rolén, Roger Marklund, Maria Marklund</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121185780</v>
+        <v>121186445</v>
       </c>
       <c r="B17" t="n">
-        <v>57348</v>
+        <v>82382</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2359,31 +2368,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2391,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>698280</v>
+        <v>698474</v>
       </c>
       <c r="R17" t="n">
-        <v>7310466</v>
+        <v>7310500</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2429,17 +2433,13 @@
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Björk med fyra bohål, varav en är nyligen avänt. Färsk sågspån på marken.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Peter Rolén, Roger Marklund, Maria Marklund</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 49168-2024 artfynd.xlsx
+++ b/artfynd/A 49168-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150814</v>
+        <v>121150820</v>
       </c>
       <c r="B2" t="n">
-        <v>90683</v>
+        <v>90717</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>698498</v>
+        <v>698117</v>
       </c>
       <c r="R2" t="n">
-        <v>7310431</v>
+        <v>7310415</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150820</v>
+        <v>121150814</v>
       </c>
       <c r="B3" t="n">
-        <v>90707</v>
+        <v>90693</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>698117</v>
+        <v>698498</v>
       </c>
       <c r="R3" t="n">
-        <v>7310415</v>
+        <v>7310431</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150819</v>
+        <v>121150817</v>
       </c>
       <c r="B4" t="n">
-        <v>90973</v>
+        <v>78601</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>698291</v>
+        <v>698483</v>
       </c>
       <c r="R4" t="n">
-        <v>7310469</v>
+        <v>7310474</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150817</v>
+        <v>121150819</v>
       </c>
       <c r="B5" t="n">
-        <v>78598</v>
+        <v>90983</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>698483</v>
+        <v>698291</v>
       </c>
       <c r="R5" t="n">
-        <v>7310474</v>
+        <v>7310469</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1122,7 +1122,7 @@
         <v>121150813</v>
       </c>
       <c r="B6" t="n">
-        <v>91998</v>
+        <v>92008</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121186127</v>
+        <v>121178213</v>
       </c>
       <c r="B7" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1278,13 +1278,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698280</v>
+        <v>698234</v>
       </c>
       <c r="R7" t="n">
-        <v>7310369</v>
+        <v>7310373</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1311,9 +1311,24 @@
           <t>2024-11-14</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121186684</v>
+        <v>120973723</v>
       </c>
       <c r="B8" t="n">
-        <v>78598</v>
+        <v>92008</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,37 +1371,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>s, Pi lm</t>
+          <t>Serpra, Serpra, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698502</v>
+        <v>698234</v>
       </c>
       <c r="R8" t="n">
-        <v>7310463</v>
+        <v>7310373</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,12 +1425,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,7 +1449,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1446,10 +1467,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121178213</v>
+        <v>120973363</v>
       </c>
       <c r="B9" t="n">
-        <v>57348</v>
+        <v>91973</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1458,36 +1479,28 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Serpra, Pi lm</t>
@@ -1524,27 +1537,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:58</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>ringhack på gran</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1564,17 +1572,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Peter Rolén, Roger Marklund, Maria Marklund</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121185600</v>
+        <v>121186681</v>
       </c>
       <c r="B10" t="n">
-        <v>57348</v>
+        <v>90697</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,31 +1595,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1619,10 +1622,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698439</v>
+        <v>698516</v>
       </c>
       <c r="R10" t="n">
-        <v>7310518</v>
+        <v>7310478</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1657,17 +1660,13 @@
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1679,17 +1678,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Peter Rolén, Roger Marklund, Maria Marklund</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120973723</v>
+        <v>121186127</v>
       </c>
       <c r="B11" t="n">
-        <v>91998</v>
+        <v>57351</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1702,34 +1701,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Serpra, Serpra, Pi lm</t>
+          <t>Serpra, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>698234</v>
+        <v>698280</v>
       </c>
       <c r="R11" t="n">
-        <v>7310373</v>
+        <v>7310369</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1756,22 +1763,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>14:47</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:47</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1791,17 +1788,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Peter Rolén, Roger Marklund, Maria Marklund</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120973363</v>
+        <v>121185780</v>
       </c>
       <c r="B12" t="n">
-        <v>91963</v>
+        <v>57351</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1810,41 +1807,49 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Serpra, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>698234</v>
+        <v>698280</v>
       </c>
       <c r="R12" t="n">
-        <v>7310373</v>
+        <v>7310466</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1868,22 +1873,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Björk med fyra bohål, varav en är nyligen avänt. Färsk sågspån på marken.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1903,17 +1903,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Peter Rolén, Roger Marklund, Maria Marklund</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121186681</v>
+        <v>121186445</v>
       </c>
       <c r="B13" t="n">
-        <v>90687</v>
+        <v>82385</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1926,21 +1926,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1953,10 +1953,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>698516</v>
+        <v>698474</v>
       </c>
       <c r="R13" t="n">
-        <v>7310478</v>
+        <v>7310500</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2016,10 +2016,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121186240</v>
+        <v>121185600</v>
       </c>
       <c r="B14" t="n">
-        <v>82382</v>
+        <v>57351</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2032,26 +2032,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2059,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>698479</v>
+        <v>698439</v>
       </c>
       <c r="R14" t="n">
-        <v>7310505</v>
+        <v>7310518</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2097,13 +2102,17 @@
           <t>2024-11-14</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2115,17 +2124,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Peter Rolén, Roger Marklund, Maria Marklund</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120972577</v>
+        <v>121186690</v>
       </c>
       <c r="B15" t="n">
-        <v>57348</v>
+        <v>78601</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2138,31 +2147,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2170,13 +2174,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>698511</v>
+        <v>698502</v>
       </c>
       <c r="R15" t="n">
-        <v>7310417</v>
+        <v>7310463</v>
       </c>
       <c r="S15" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2200,17 +2204,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>ringhack på gran</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2219,6 +2218,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2237,10 +2237,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121185780</v>
+        <v>121186240</v>
       </c>
       <c r="B16" t="n">
-        <v>57348</v>
+        <v>82385</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2253,31 +2253,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2285,10 +2280,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>698280</v>
+        <v>698479</v>
       </c>
       <c r="R16" t="n">
-        <v>7310466</v>
+        <v>7310505</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2323,17 +2318,13 @@
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Björk med fyra bohål, varav en är nyligen avänt. Färsk sågspån på marken.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2345,17 +2336,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Peter Rolén, Roger Marklund, Maria Marklund</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121186445</v>
+        <v>120972577</v>
       </c>
       <c r="B17" t="n">
-        <v>82382</v>
+        <v>57351</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2368,26 +2359,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2395,13 +2391,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>698474</v>
+        <v>698511</v>
       </c>
       <c r="R17" t="n">
-        <v>7310500</v>
+        <v>7310417</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2425,12 +2421,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2439,7 +2440,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2461,7 +2461,7 @@
         <v>121202112</v>
       </c>
       <c r="B18" t="n">
-        <v>90705</v>
+        <v>90715</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>121202119</v>
       </c>
       <c r="B19" t="n">
-        <v>90687</v>
+        <v>90697</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 49168-2024 artfynd.xlsx
+++ b/artfynd/A 49168-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150820</v>
+        <v>121150817</v>
       </c>
       <c r="B2" t="n">
-        <v>90717</v>
+        <v>78601</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>698117</v>
+        <v>698483</v>
       </c>
       <c r="R2" t="n">
-        <v>7310415</v>
+        <v>7310474</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150814</v>
+        <v>121150819</v>
       </c>
       <c r="B3" t="n">
-        <v>90693</v>
+        <v>90983</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>698498</v>
+        <v>698291</v>
       </c>
       <c r="R3" t="n">
-        <v>7310431</v>
+        <v>7310469</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150817</v>
+        <v>121150813</v>
       </c>
       <c r="B4" t="n">
-        <v>78601</v>
+        <v>92008</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>698483</v>
+        <v>698338</v>
       </c>
       <c r="R4" t="n">
-        <v>7310474</v>
+        <v>7310194</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150819</v>
+        <v>121150820</v>
       </c>
       <c r="B5" t="n">
-        <v>90983</v>
+        <v>90717</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>698291</v>
+        <v>698117</v>
       </c>
       <c r="R5" t="n">
-        <v>7310469</v>
+        <v>7310415</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121150813</v>
+        <v>121150814</v>
       </c>
       <c r="B6" t="n">
-        <v>92008</v>
+        <v>90693</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698338</v>
+        <v>698498</v>
       </c>
       <c r="R6" t="n">
-        <v>7310194</v>
+        <v>7310431</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121178213</v>
+        <v>120973723</v>
       </c>
       <c r="B7" t="n">
-        <v>57351</v>
+        <v>92008</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,35 +1246,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Serpra, Pi lm</t>
+          <t>Serpra, Serpra, Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -1284,7 +1276,7 @@
         <v>7310373</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1308,27 +1300,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:58</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>ringhack på gran</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,17 +1335,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Peter Rolén, Roger Marklund, Maria Marklund</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120973723</v>
+        <v>121186127</v>
       </c>
       <c r="B8" t="n">
-        <v>92008</v>
+        <v>57351</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,34 +1358,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Serpra, Serpra, Pi lm</t>
+          <t>Serpra, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698234</v>
+        <v>698280</v>
       </c>
       <c r="R8" t="n">
-        <v>7310373</v>
+        <v>7310369</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,22 +1420,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:47</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:47</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1460,17 +1445,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Peter Rolén, Roger Marklund, Maria Marklund</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120973363</v>
+        <v>121186445</v>
       </c>
       <c r="B9" t="n">
-        <v>91973</v>
+        <v>82385</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,41 +1464,44 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Serpra, Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>698234</v>
+        <v>698474</v>
       </c>
       <c r="R9" t="n">
-        <v>7310373</v>
+        <v>7310500</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1537,22 +1525,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,6 +1539,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1579,10 +1558,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121186681</v>
+        <v>120972577</v>
       </c>
       <c r="B10" t="n">
-        <v>90697</v>
+        <v>57351</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1595,26 +1574,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1622,13 +1606,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698516</v>
+        <v>698511</v>
       </c>
       <c r="R10" t="n">
-        <v>7310478</v>
+        <v>7310417</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1652,12 +1636,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1666,7 +1655,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1685,7 +1673,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121186127</v>
+        <v>121185600</v>
       </c>
       <c r="B11" t="n">
         <v>57351</v>
@@ -1723,7 +1711,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1733,10 +1721,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>698280</v>
+        <v>698439</v>
       </c>
       <c r="R11" t="n">
-        <v>7310369</v>
+        <v>7310518</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1769,6 +1757,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1788,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121185780</v>
+        <v>121186681</v>
       </c>
       <c r="B12" t="n">
-        <v>57351</v>
+        <v>90697</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,31 +1804,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1843,10 +1831,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>698280</v>
+        <v>698516</v>
       </c>
       <c r="R12" t="n">
-        <v>7310466</v>
+        <v>7310478</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1881,17 +1869,13 @@
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Björk med fyra bohål, varav en är nyligen avänt. Färsk sågspån på marken.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1903,14 +1887,14 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Peter Rolén, Roger Marklund, Maria Marklund</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121186445</v>
+        <v>121186240</v>
       </c>
       <c r="B13" t="n">
         <v>82385</v>
@@ -1953,10 +1937,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>698474</v>
+        <v>698479</v>
       </c>
       <c r="R13" t="n">
-        <v>7310500</v>
+        <v>7310505</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2016,10 +2000,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121185600</v>
+        <v>120973363</v>
       </c>
       <c r="B14" t="n">
-        <v>57351</v>
+        <v>91973</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2028,49 +2012,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Serpra, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>698439</v>
+        <v>698234</v>
       </c>
       <c r="R14" t="n">
-        <v>7310518</v>
+        <v>7310373</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2094,17 +2070,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2124,17 +2105,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Peter Rolén, Roger Marklund, Maria Marklund</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121186690</v>
+        <v>121185780</v>
       </c>
       <c r="B15" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2147,26 +2128,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2174,10 +2160,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>698502</v>
+        <v>698280</v>
       </c>
       <c r="R15" t="n">
-        <v>7310463</v>
+        <v>7310466</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2212,13 +2198,17 @@
           <t>2024-11-14</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Björk med fyra bohål, varav en är nyligen avänt. Färsk sågspån på marken.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2230,17 +2220,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Peter Rolén, Roger Marklund, Maria Marklund</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121186240</v>
+        <v>121186684</v>
       </c>
       <c r="B16" t="n">
-        <v>82385</v>
+        <v>78601</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2253,21 +2243,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2276,14 +2266,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Serpra, Pi lm</t>
+          <t>s, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>698479</v>
+        <v>698502</v>
       </c>
       <c r="R16" t="n">
-        <v>7310505</v>
+        <v>7310463</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2343,7 +2333,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120972577</v>
+        <v>121178213</v>
       </c>
       <c r="B17" t="n">
         <v>57351</v>
@@ -2391,13 +2381,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>698511</v>
+        <v>698234</v>
       </c>
       <c r="R17" t="n">
-        <v>7310417</v>
+        <v>7310373</v>
       </c>
       <c r="S17" t="n">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2421,12 +2411,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Peter Rolén, Roger Marklund, Maria Marklund</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 49168-2024 artfynd.xlsx
+++ b/artfynd/A 49168-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150817</v>
+        <v>121150814</v>
       </c>
       <c r="B2" t="n">
-        <v>78601</v>
+        <v>90705</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>698483</v>
+        <v>698498</v>
       </c>
       <c r="R2" t="n">
-        <v>7310474</v>
+        <v>7310431</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150819</v>
+        <v>121150820</v>
       </c>
       <c r="B3" t="n">
-        <v>90983</v>
+        <v>90729</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>698291</v>
+        <v>698117</v>
       </c>
       <c r="R3" t="n">
-        <v>7310469</v>
+        <v>7310415</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150813</v>
+        <v>121150819</v>
       </c>
       <c r="B4" t="n">
-        <v>92008</v>
+        <v>90995</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>698338</v>
+        <v>698291</v>
       </c>
       <c r="R4" t="n">
-        <v>7310194</v>
+        <v>7310469</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150820</v>
+        <v>121150813</v>
       </c>
       <c r="B5" t="n">
-        <v>90717</v>
+        <v>92020</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>698117</v>
+        <v>698338</v>
       </c>
       <c r="R5" t="n">
-        <v>7310415</v>
+        <v>7310194</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121150814</v>
+        <v>121150817</v>
       </c>
       <c r="B6" t="n">
-        <v>90693</v>
+        <v>78604</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698498</v>
+        <v>698483</v>
       </c>
       <c r="R6" t="n">
-        <v>7310431</v>
+        <v>7310474</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120973723</v>
+        <v>121186684</v>
       </c>
       <c r="B7" t="n">
-        <v>92008</v>
+        <v>78604</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,34 +1246,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Serpra, Serpra, Pi lm</t>
+          <t>s, Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698234</v>
+        <v>698502</v>
       </c>
       <c r="R7" t="n">
-        <v>7310373</v>
+        <v>7310463</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,22 +1303,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:47</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:47</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,6 +1317,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1342,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121186127</v>
+        <v>121186681</v>
       </c>
       <c r="B8" t="n">
-        <v>57351</v>
+        <v>90709</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1358,31 +1352,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1390,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698280</v>
+        <v>698516</v>
       </c>
       <c r="R8" t="n">
-        <v>7310369</v>
+        <v>7310478</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,6 +1423,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1445,17 +1435,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Peter Rolén, Roger Marklund, Maria Marklund</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121186445</v>
+        <v>121185780</v>
       </c>
       <c r="B9" t="n">
-        <v>82385</v>
+        <v>57351</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,26 +1458,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1495,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>698474</v>
+        <v>698280</v>
       </c>
       <c r="R9" t="n">
-        <v>7310500</v>
+        <v>7310466</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,13 +1528,17 @@
           <t>2024-11-14</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Björk med fyra bohål, varav en är nyligen avänt. Färsk sågspån på marken.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1551,7 +1550,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Peter Rolén, Roger Marklund, Maria Marklund</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1673,10 +1672,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121185600</v>
+        <v>120973363</v>
       </c>
       <c r="B11" t="n">
-        <v>57351</v>
+        <v>91985</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1685,49 +1684,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Serpra, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>698439</v>
+        <v>698234</v>
       </c>
       <c r="R11" t="n">
-        <v>7310518</v>
+        <v>7310373</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1751,17 +1742,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1781,17 +1777,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Peter Rolén, Roger Marklund, Maria Marklund</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121186681</v>
+        <v>121186240</v>
       </c>
       <c r="B12" t="n">
-        <v>90697</v>
+        <v>82388</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1804,21 +1800,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1831,10 +1827,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>698516</v>
+        <v>698479</v>
       </c>
       <c r="R12" t="n">
-        <v>7310478</v>
+        <v>7310505</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1894,10 +1890,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121186240</v>
+        <v>120973723</v>
       </c>
       <c r="B13" t="n">
-        <v>82385</v>
+        <v>92020</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1910,37 +1906,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>5966</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Serpra, Pi lm</t>
+          <t>Serpra, Serpra, Pi lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>698479</v>
+        <v>698234</v>
       </c>
       <c r="R13" t="n">
-        <v>7310505</v>
+        <v>7310373</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,12 +1960,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1981,7 +1984,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2000,10 +2002,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120973363</v>
+        <v>121185600</v>
       </c>
       <c r="B14" t="n">
-        <v>91973</v>
+        <v>57351</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2012,41 +2014,49 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Serpra, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>698234</v>
+        <v>698439</v>
       </c>
       <c r="R14" t="n">
-        <v>7310373</v>
+        <v>7310518</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2070,22 +2080,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2105,14 +2110,14 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Peter Rolén, Roger Marklund, Maria Marklund</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121185780</v>
+        <v>121178213</v>
       </c>
       <c r="B15" t="n">
         <v>57351</v>
@@ -2150,7 +2155,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2160,13 +2165,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>698280</v>
+        <v>698234</v>
       </c>
       <c r="R15" t="n">
-        <v>7310466</v>
+        <v>7310373</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2193,14 +2198,24 @@
           <t>2024-11-14</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-11-14</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Björk med fyra bohål, varav en är nyligen avänt. Färsk sågspån på marken.</t>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2227,10 +2242,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121186684</v>
+        <v>121186445</v>
       </c>
       <c r="B16" t="n">
-        <v>78601</v>
+        <v>82388</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2243,21 +2258,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2266,14 +2281,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>s, Pi lm</t>
+          <t>Serpra, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>698502</v>
+        <v>698474</v>
       </c>
       <c r="R16" t="n">
-        <v>7310463</v>
+        <v>7310500</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2333,7 +2348,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121178213</v>
+        <v>121186127</v>
       </c>
       <c r="B17" t="n">
         <v>57351</v>
@@ -2371,7 +2386,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2381,13 +2396,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>698234</v>
+        <v>698280</v>
       </c>
       <c r="R17" t="n">
-        <v>7310373</v>
+        <v>7310369</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2414,24 +2429,9 @@
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2458,10 +2458,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121202112</v>
+        <v>121202119</v>
       </c>
       <c r="B18" t="n">
-        <v>90715</v>
+        <v>90709</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2474,21 +2474,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2501,10 +2501,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>698257</v>
+        <v>698528</v>
       </c>
       <c r="R18" t="n">
-        <v>7310346</v>
+        <v>7310459</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121202119</v>
+        <v>121202112</v>
       </c>
       <c r="B19" t="n">
-        <v>90697</v>
+        <v>90727</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2580,21 +2580,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2607,10 +2607,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>698528</v>
+        <v>698257</v>
       </c>
       <c r="R19" t="n">
-        <v>7310459</v>
+        <v>7310346</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>

--- a/artfynd/A 49168-2024 artfynd.xlsx
+++ b/artfynd/A 49168-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150814</v>
+        <v>121150819</v>
       </c>
       <c r="B2" t="n">
-        <v>90705</v>
+        <v>90996</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>698498</v>
+        <v>698291</v>
       </c>
       <c r="R2" t="n">
-        <v>7310431</v>
+        <v>7310469</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150820</v>
+        <v>121150814</v>
       </c>
       <c r="B3" t="n">
-        <v>90729</v>
+        <v>90706</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>698117</v>
+        <v>698498</v>
       </c>
       <c r="R3" t="n">
-        <v>7310415</v>
+        <v>7310431</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150819</v>
+        <v>121150817</v>
       </c>
       <c r="B4" t="n">
-        <v>90995</v>
+        <v>78604</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>698291</v>
+        <v>698483</v>
       </c>
       <c r="R4" t="n">
-        <v>7310469</v>
+        <v>7310474</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1011,7 +1011,7 @@
         <v>121150813</v>
       </c>
       <c r="B5" t="n">
-        <v>92020</v>
+        <v>92021</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121150817</v>
+        <v>121150820</v>
       </c>
       <c r="B6" t="n">
-        <v>78604</v>
+        <v>90730</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698483</v>
+        <v>698117</v>
       </c>
       <c r="R6" t="n">
-        <v>7310474</v>
+        <v>7310415</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121186684</v>
+        <v>121185600</v>
       </c>
       <c r="B7" t="n">
-        <v>78604</v>
+        <v>57351</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,37 +1246,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>s, Pi lm</t>
+          <t>Serpra, Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698502</v>
+        <v>698439</v>
       </c>
       <c r="R7" t="n">
-        <v>7310463</v>
+        <v>7310518</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,13 +1316,17 @@
           <t>2024-11-14</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1329,17 +1338,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Peter Rolén, Roger Marklund, Maria Marklund</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121186681</v>
+        <v>121186240</v>
       </c>
       <c r="B8" t="n">
-        <v>90709</v>
+        <v>82388</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1352,21 +1361,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1379,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698516</v>
+        <v>698479</v>
       </c>
       <c r="R8" t="n">
-        <v>7310478</v>
+        <v>7310505</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1451,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121185780</v>
+        <v>120972577</v>
       </c>
       <c r="B9" t="n">
         <v>57351</v>
@@ -1480,7 +1489,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1490,13 +1499,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>698280</v>
+        <v>698511</v>
       </c>
       <c r="R9" t="n">
-        <v>7310466</v>
+        <v>7310417</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1520,17 +1529,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Björk med fyra bohål, varav en är nyligen avänt. Färsk sågspån på marken.</t>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1550,17 +1559,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Peter Rolén, Roger Marklund, Maria Marklund</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120972577</v>
+        <v>121186690</v>
       </c>
       <c r="B10" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1573,31 +1582,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1605,13 +1609,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698511</v>
+        <v>698502</v>
       </c>
       <c r="R10" t="n">
-        <v>7310417</v>
+        <v>7310463</v>
       </c>
       <c r="S10" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1635,17 +1639,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>ringhack på gran</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1654,6 +1653,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1672,10 +1672,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120973363</v>
+        <v>121186681</v>
       </c>
       <c r="B11" t="n">
-        <v>91985</v>
+        <v>90710</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1684,41 +1684,44 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Serpra, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>698234</v>
+        <v>698516</v>
       </c>
       <c r="R11" t="n">
-        <v>7310373</v>
+        <v>7310478</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1742,22 +1745,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1766,6 +1759,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1784,10 +1778,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121186240</v>
+        <v>120973723</v>
       </c>
       <c r="B12" t="n">
-        <v>82388</v>
+        <v>92021</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1800,37 +1794,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>5966</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Serpra, Pi lm</t>
+          <t>Serpra, Serpra, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>698479</v>
+        <v>698234</v>
       </c>
       <c r="R12" t="n">
-        <v>7310505</v>
+        <v>7310373</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,12 +1848,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1871,7 +1872,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1890,10 +1890,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120973723</v>
+        <v>121186445</v>
       </c>
       <c r="B13" t="n">
-        <v>92020</v>
+        <v>82388</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1906,34 +1906,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5966</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Serpra, Serpra, Pi lm</t>
+          <t>Serpra, Pi lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>698234</v>
+        <v>698474</v>
       </c>
       <c r="R13" t="n">
-        <v>7310373</v>
+        <v>7310500</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1960,22 +1963,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:47</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:47</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1984,6 +1977,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2002,10 +1996,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121185600</v>
+        <v>120973363</v>
       </c>
       <c r="B14" t="n">
-        <v>57351</v>
+        <v>91986</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2014,49 +2008,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Serpra, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>698439</v>
+        <v>698234</v>
       </c>
       <c r="R14" t="n">
-        <v>7310518</v>
+        <v>7310373</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2080,17 +2066,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2110,7 +2101,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Peter Rolén, Roger Marklund, Maria Marklund</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2242,10 +2233,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121186445</v>
+        <v>121185780</v>
       </c>
       <c r="B16" t="n">
-        <v>82388</v>
+        <v>57351</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2258,26 +2249,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2285,10 +2281,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>698474</v>
+        <v>698280</v>
       </c>
       <c r="R16" t="n">
-        <v>7310500</v>
+        <v>7310466</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2323,13 +2319,17 @@
           <t>2024-11-14</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Björk med fyra bohål, varav en är nyligen avänt. Färsk sågspån på marken.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Peter Rolén, Roger Marklund, Maria Marklund</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2458,10 +2458,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121202119</v>
+        <v>121202112</v>
       </c>
       <c r="B18" t="n">
-        <v>90709</v>
+        <v>90728</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2474,21 +2474,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2501,10 +2501,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>698528</v>
+        <v>698257</v>
       </c>
       <c r="R18" t="n">
-        <v>7310459</v>
+        <v>7310346</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121202112</v>
+        <v>121202119</v>
       </c>
       <c r="B19" t="n">
-        <v>90727</v>
+        <v>90710</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2580,21 +2580,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2607,10 +2607,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>698257</v>
+        <v>698528</v>
       </c>
       <c r="R19" t="n">
-        <v>7310346</v>
+        <v>7310459</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>

--- a/artfynd/A 49168-2024 artfynd.xlsx
+++ b/artfynd/A 49168-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150819</v>
+        <v>121150820</v>
       </c>
       <c r="B2" t="n">
-        <v>90996</v>
+        <v>90733</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>698291</v>
+        <v>698117</v>
       </c>
       <c r="R2" t="n">
-        <v>7310469</v>
+        <v>7310415</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150814</v>
+        <v>121150819</v>
       </c>
       <c r="B3" t="n">
-        <v>90706</v>
+        <v>90999</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>698498</v>
+        <v>698291</v>
       </c>
       <c r="R3" t="n">
-        <v>7310431</v>
+        <v>7310469</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -900,7 +900,7 @@
         <v>121150817</v>
       </c>
       <c r="B4" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>121150813</v>
       </c>
       <c r="B5" t="n">
-        <v>92021</v>
+        <v>92024</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121150820</v>
+        <v>121150814</v>
       </c>
       <c r="B6" t="n">
-        <v>90730</v>
+        <v>90709</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698117</v>
+        <v>698498</v>
       </c>
       <c r="R6" t="n">
-        <v>7310415</v>
+        <v>7310431</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121185600</v>
+        <v>120973723</v>
       </c>
       <c r="B7" t="n">
-        <v>57351</v>
+        <v>92024</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,42 +1246,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Serpra, Pi lm</t>
+          <t>Serpra, Serpra, Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698439</v>
+        <v>698234</v>
       </c>
       <c r="R7" t="n">
-        <v>7310518</v>
+        <v>7310373</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,17 +1300,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1338,17 +1335,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Peter Rolén, Roger Marklund, Maria Marklund</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121186240</v>
+        <v>121186445</v>
       </c>
       <c r="B8" t="n">
-        <v>82388</v>
+        <v>82391</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698479</v>
+        <v>698474</v>
       </c>
       <c r="R8" t="n">
-        <v>7310505</v>
+        <v>7310500</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,10 +1448,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120972577</v>
+        <v>121185600</v>
       </c>
       <c r="B9" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,13 +1496,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>698511</v>
+        <v>698439</v>
       </c>
       <c r="R9" t="n">
-        <v>7310417</v>
+        <v>7310518</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1529,17 +1526,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack på gran</t>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,17 +1556,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Peter Rolén, Roger Marklund, Maria Marklund</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121186690</v>
+        <v>121185780</v>
       </c>
       <c r="B10" t="n">
-        <v>78604</v>
+        <v>57354</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1582,26 +1579,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1609,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698502</v>
+        <v>698280</v>
       </c>
       <c r="R10" t="n">
-        <v>7310463</v>
+        <v>7310466</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1647,13 +1649,17 @@
           <t>2024-11-14</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Björk med fyra bohål, varav en är nyligen avänt. Färsk sågspån på marken.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1665,17 +1671,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Peter Rolén, Roger Marklund, Maria Marklund</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121186681</v>
+        <v>120972577</v>
       </c>
       <c r="B11" t="n">
-        <v>90710</v>
+        <v>57354</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1688,26 +1694,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1715,13 +1726,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>698516</v>
+        <v>698511</v>
       </c>
       <c r="R11" t="n">
-        <v>7310478</v>
+        <v>7310417</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1745,12 +1756,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,7 +1775,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1778,10 +1793,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120973723</v>
+        <v>120973363</v>
       </c>
       <c r="B12" t="n">
-        <v>92021</v>
+        <v>91989</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1790,31 +1805,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Serpra, Serpra, Pi lm</t>
+          <t>Serpra, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
@@ -1824,7 +1839,7 @@
         <v>7310373</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1853,7 +1868,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1863,7 +1878,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1890,10 +1905,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121186445</v>
+        <v>121186240</v>
       </c>
       <c r="B13" t="n">
-        <v>82388</v>
+        <v>82391</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1933,10 +1948,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>698474</v>
+        <v>698479</v>
       </c>
       <c r="R13" t="n">
-        <v>7310500</v>
+        <v>7310505</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1996,10 +2011,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120973363</v>
+        <v>121186690</v>
       </c>
       <c r="B14" t="n">
-        <v>91986</v>
+        <v>78607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2008,41 +2023,44 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Serpra, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>698234</v>
+        <v>698502</v>
       </c>
       <c r="R14" t="n">
-        <v>7310373</v>
+        <v>7310463</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2066,22 +2084,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2090,6 +2098,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2108,10 +2117,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121178213</v>
+        <v>121186127</v>
       </c>
       <c r="B15" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2146,7 +2155,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2156,13 +2165,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>698234</v>
+        <v>698280</v>
       </c>
       <c r="R15" t="n">
-        <v>7310373</v>
+        <v>7310369</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2189,24 +2198,9 @@
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2233,10 +2227,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121185780</v>
+        <v>121186681</v>
       </c>
       <c r="B16" t="n">
-        <v>57351</v>
+        <v>90713</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2249,31 +2243,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2281,10 +2270,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>698280</v>
+        <v>698516</v>
       </c>
       <c r="R16" t="n">
-        <v>7310466</v>
+        <v>7310478</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2319,17 +2308,13 @@
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Björk med fyra bohål, varav en är nyligen avänt. Färsk sågspån på marken.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2341,17 +2326,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Peter Rolén, Roger Marklund, Maria Marklund</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121186127</v>
+        <v>121178213</v>
       </c>
       <c r="B17" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2386,7 +2371,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2396,13 +2381,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>698280</v>
+        <v>698234</v>
       </c>
       <c r="R17" t="n">
-        <v>7310369</v>
+        <v>7310373</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2429,9 +2414,24 @@
           <t>2024-11-14</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2458,10 +2458,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121202112</v>
+        <v>121202119</v>
       </c>
       <c r="B18" t="n">
-        <v>90728</v>
+        <v>90713</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2474,21 +2474,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2501,10 +2501,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>698257</v>
+        <v>698528</v>
       </c>
       <c r="R18" t="n">
-        <v>7310346</v>
+        <v>7310459</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121202119</v>
+        <v>121202112</v>
       </c>
       <c r="B19" t="n">
-        <v>90710</v>
+        <v>90731</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2580,21 +2580,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2607,10 +2607,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>698528</v>
+        <v>698257</v>
       </c>
       <c r="R19" t="n">
-        <v>7310459</v>
+        <v>7310346</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>

--- a/artfynd/A 49168-2024 artfynd.xlsx
+++ b/artfynd/A 49168-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150820</v>
+        <v>121150813</v>
       </c>
       <c r="B2" t="n">
-        <v>90733</v>
+        <v>92024</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>698117</v>
+        <v>698338</v>
       </c>
       <c r="R2" t="n">
-        <v>7310415</v>
+        <v>7310194</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150813</v>
+        <v>121150814</v>
       </c>
       <c r="B5" t="n">
-        <v>92024</v>
+        <v>90709</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>698338</v>
+        <v>698498</v>
       </c>
       <c r="R5" t="n">
-        <v>7310194</v>
+        <v>7310431</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121150814</v>
+        <v>121150820</v>
       </c>
       <c r="B6" t="n">
-        <v>90709</v>
+        <v>90733</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698498</v>
+        <v>698117</v>
       </c>
       <c r="R6" t="n">
-        <v>7310431</v>
+        <v>7310415</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120973723</v>
+        <v>121185600</v>
       </c>
       <c r="B7" t="n">
-        <v>92024</v>
+        <v>57354</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,34 +1246,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Serpra, Serpra, Pi lm</t>
+          <t>Serpra, Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698234</v>
+        <v>698439</v>
       </c>
       <c r="R7" t="n">
-        <v>7310373</v>
+        <v>7310518</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,22 +1308,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:47</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:47</t>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,17 +1338,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Peter Rolén, Roger Marklund, Maria Marklund</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121186445</v>
+        <v>121178213</v>
       </c>
       <c r="B8" t="n">
-        <v>82391</v>
+        <v>57354</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1358,26 +1361,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1385,13 +1393,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698474</v>
+        <v>698234</v>
       </c>
       <c r="R8" t="n">
-        <v>7310500</v>
+        <v>7310373</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1418,18 +1426,32 @@
           <t>2024-11-14</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-14</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1441,14 +1463,14 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Peter Rolén, Roger Marklund, Maria Marklund</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121185600</v>
+        <v>120972577</v>
       </c>
       <c r="B9" t="n">
         <v>57354</v>
@@ -1496,13 +1518,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>698439</v>
+        <v>698511</v>
       </c>
       <c r="R9" t="n">
-        <v>7310518</v>
+        <v>7310417</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1526,17 +1548,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack på tall</t>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,17 +1578,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Peter Rolén, Roger Marklund, Maria Marklund</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121185780</v>
+        <v>121186445</v>
       </c>
       <c r="B10" t="n">
-        <v>57354</v>
+        <v>82391</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1579,31 +1601,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1611,10 +1628,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698280</v>
+        <v>698474</v>
       </c>
       <c r="R10" t="n">
-        <v>7310466</v>
+        <v>7310500</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1649,17 +1666,13 @@
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Björk med fyra bohål, varav en är nyligen avänt. Färsk sågspån på marken.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1671,17 +1684,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Peter Rolén, Roger Marklund, Maria Marklund</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120972577</v>
+        <v>121186690</v>
       </c>
       <c r="B11" t="n">
-        <v>57354</v>
+        <v>78607</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1694,31 +1707,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1726,13 +1734,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>698511</v>
+        <v>698502</v>
       </c>
       <c r="R11" t="n">
-        <v>7310417</v>
+        <v>7310463</v>
       </c>
       <c r="S11" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1756,17 +1764,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>ringhack på gran</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1775,6 +1778,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1793,10 +1797,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120973363</v>
+        <v>121186240</v>
       </c>
       <c r="B12" t="n">
-        <v>91989</v>
+        <v>82391</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1805,41 +1809,44 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Serpra, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>698234</v>
+        <v>698479</v>
       </c>
       <c r="R12" t="n">
-        <v>7310373</v>
+        <v>7310505</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1863,22 +1870,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1887,6 +1884,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1905,10 +1903,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121186240</v>
+        <v>121185780</v>
       </c>
       <c r="B13" t="n">
-        <v>82391</v>
+        <v>57354</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1921,26 +1919,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1948,10 +1951,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>698479</v>
+        <v>698280</v>
       </c>
       <c r="R13" t="n">
-        <v>7310505</v>
+        <v>7310466</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1986,13 +1989,17 @@
           <t>2024-11-14</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Björk med fyra bohål, varav en är nyligen avänt. Färsk sågspån på marken.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2004,17 +2011,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Peter Rolén, Roger Marklund, Maria Marklund</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121186690</v>
+        <v>120973363</v>
       </c>
       <c r="B14" t="n">
-        <v>78607</v>
+        <v>91989</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2023,44 +2030,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Serpra, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>698502</v>
+        <v>698234</v>
       </c>
       <c r="R14" t="n">
-        <v>7310463</v>
+        <v>7310373</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2084,12 +2088,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2098,7 +2112,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2333,10 +2346,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121178213</v>
+        <v>120973723</v>
       </c>
       <c r="B17" t="n">
-        <v>57354</v>
+        <v>92024</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2349,35 +2362,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Serpra, Pi lm</t>
+          <t>Serpra, Serpra, Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
@@ -2387,7 +2392,7 @@
         <v>7310373</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2411,27 +2416,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:58</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>ringhack på gran</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Peter Rolén, Roger Marklund, Maria Marklund</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 49168-2024 artfynd.xlsx
+++ b/artfynd/A 49168-2024 artfynd.xlsx
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121185600</v>
+        <v>121178213</v>
       </c>
       <c r="B7" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,13 +1278,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698439</v>
+        <v>698234</v>
       </c>
       <c r="R7" t="n">
-        <v>7310518</v>
+        <v>7310373</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1311,14 +1311,24 @@
           <t>2024-11-14</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-14</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack på tall</t>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121178213</v>
+        <v>121185600</v>
       </c>
       <c r="B8" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,13 +1403,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698234</v>
+        <v>698439</v>
       </c>
       <c r="R8" t="n">
-        <v>7310373</v>
+        <v>7310518</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,24 +1436,14 @@
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack på gran</t>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120972577</v>
+        <v>121185780</v>
       </c>
       <c r="B9" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1518,13 +1518,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>698511</v>
+        <v>698280</v>
       </c>
       <c r="R9" t="n">
-        <v>7310417</v>
+        <v>7310466</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1548,17 +1548,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack på gran</t>
+          <t>Björk med fyra bohål, varav en är nyligen avänt. Färsk sågspån på marken.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,17 +1578,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Peter Rolén, Roger Marklund, Maria Marklund</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121186445</v>
+        <v>121186690</v>
       </c>
       <c r="B10" t="n">
-        <v>82391</v>
+        <v>78608</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,21 +1601,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698474</v>
+        <v>698502</v>
       </c>
       <c r="R10" t="n">
-        <v>7310500</v>
+        <v>7310463</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1691,10 +1691,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121186690</v>
+        <v>120973363</v>
       </c>
       <c r="B11" t="n">
-        <v>78607</v>
+        <v>91995</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1703,44 +1703,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Serpra, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>698502</v>
+        <v>698234</v>
       </c>
       <c r="R11" t="n">
-        <v>7310463</v>
+        <v>7310373</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1764,12 +1761,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1778,7 +1785,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1797,10 +1803,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121186240</v>
+        <v>121186127</v>
       </c>
       <c r="B12" t="n">
-        <v>82391</v>
+        <v>57355</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1813,26 +1819,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1840,10 +1851,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>698479</v>
+        <v>698280</v>
       </c>
       <c r="R12" t="n">
-        <v>7310505</v>
+        <v>7310369</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1884,7 +1895,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1896,17 +1906,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Peter Rolén, Roger Marklund, Maria Marklund</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121185780</v>
+        <v>121186445</v>
       </c>
       <c r="B13" t="n">
-        <v>57354</v>
+        <v>82392</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,31 +1929,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1951,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>698280</v>
+        <v>698474</v>
       </c>
       <c r="R13" t="n">
-        <v>7310466</v>
+        <v>7310500</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1989,17 +1994,13 @@
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Björk med fyra bohål, varav en är nyligen avänt. Färsk sågspån på marken.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2011,17 +2012,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Peter Rolén, Roger Marklund, Maria Marklund</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120973363</v>
+        <v>121186240</v>
       </c>
       <c r="B14" t="n">
-        <v>91989</v>
+        <v>82392</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2030,41 +2031,44 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Serpra, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>698234</v>
+        <v>698479</v>
       </c>
       <c r="R14" t="n">
-        <v>7310373</v>
+        <v>7310505</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2088,22 +2092,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2112,6 +2106,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2130,10 +2125,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121186127</v>
+        <v>120973723</v>
       </c>
       <c r="B15" t="n">
-        <v>57354</v>
+        <v>92030</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2146,42 +2141,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Serpra, Pi lm</t>
+          <t>Serpra, Serpra, Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>698280</v>
+        <v>698234</v>
       </c>
       <c r="R15" t="n">
-        <v>7310369</v>
+        <v>7310373</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2208,12 +2195,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2233,7 +2230,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Peter Rolén, Roger Marklund, Maria Marklund</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2243,7 +2240,7 @@
         <v>121186681</v>
       </c>
       <c r="B16" t="n">
-        <v>90713</v>
+        <v>90719</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2346,10 +2343,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120973723</v>
+        <v>120972577</v>
       </c>
       <c r="B17" t="n">
-        <v>92024</v>
+        <v>57355</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2362,37 +2359,45 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5966</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Serpra, Serpra, Pi lm</t>
+          <t>Serpra, Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>698234</v>
+        <v>698511</v>
       </c>
       <c r="R17" t="n">
-        <v>7310373</v>
+        <v>7310417</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2419,19 +2424,14 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>14:47</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2461,7 +2461,7 @@
         <v>121202119</v>
       </c>
       <c r="B18" t="n">
-        <v>90713</v>
+        <v>90719</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>121202112</v>
       </c>
       <c r="B19" t="n">
-        <v>90731</v>
+        <v>90737</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 49168-2024 artfynd.xlsx
+++ b/artfynd/A 49168-2024 artfynd.xlsx
@@ -1803,10 +1803,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121186127</v>
+        <v>121186445</v>
       </c>
       <c r="B12" t="n">
-        <v>57355</v>
+        <v>82392</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1819,31 +1819,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1851,10 +1846,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>698280</v>
+        <v>698474</v>
       </c>
       <c r="R12" t="n">
-        <v>7310369</v>
+        <v>7310500</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,6 +1890,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1906,17 +1902,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Peter Rolén, Roger Marklund, Maria Marklund</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121186445</v>
+        <v>121186127</v>
       </c>
       <c r="B13" t="n">
-        <v>82392</v>
+        <v>57355</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1929,26 +1925,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1956,10 +1957,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>698474</v>
+        <v>698280</v>
       </c>
       <c r="R13" t="n">
-        <v>7310500</v>
+        <v>7310369</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2000,7 +2001,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Peter Rolén, Roger Marklund, Maria Marklund</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 49168-2024 artfynd.xlsx
+++ b/artfynd/A 49168-2024 artfynd.xlsx
@@ -2461,7 +2461,7 @@
         <v>121202119</v>
       </c>
       <c r="B18" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>121202112</v>
       </c>
       <c r="B19" t="n">
-        <v>90737</v>
+        <v>90738</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 49168-2024 artfynd.xlsx
+++ b/artfynd/A 49168-2024 artfynd.xlsx
@@ -1473,11 +1473,11 @@
         <v>121185780</v>
       </c>
       <c r="B9" t="n">
-        <v>57355</v>
+        <v>57384</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">

--- a/artfynd/A 49168-2024 artfynd.xlsx
+++ b/artfynd/A 49168-2024 artfynd.xlsx
@@ -1473,7 +1473,7 @@
         <v>121185780</v>
       </c>
       <c r="B9" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
